--- a/Auxiliary tool/bin/Debug/ExamA02Score.xlsx
+++ b/Auxiliary tool/bin/Debug/ExamA02Score.xlsx
@@ -1777,7 +1777,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>坂本</t>
+          <t>山田太郎</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2876,7 +2876,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>柊镜</t>
+          <t>日下部美纱绪</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3033,7 +3033,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>柊司</t>
+          <t>樱庭光</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6801,7 +6801,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>惠惠</t>
+          <t>泽村英梨梨</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7429,7 +7429,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>雷姆</t>
+          <t>安娜塔西亚</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7586,7 +7586,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>拉姆</t>
+          <t>法兰黛莉卡</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7743,7 +7743,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>桐人</t>
+          <t>优吉欧</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -8057,7 +8057,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>诗乃</t>
+          <t>桐谷直叶</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -8214,7 +8214,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>莉法</t>
+          <t>结城明日奈</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -9313,7 +9313,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>艾伦</t>
+          <t>艾伦耶格尔</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -9470,7 +9470,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>三笠</t>
+          <t>三笠阿克曼</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -10412,7 +10412,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>路飞</t>
+          <t>蒙奇路飞</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -10569,7 +10569,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>索隆</t>
+          <t>罗罗诺亚</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -10726,7 +10726,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>娜美</t>
+          <t>妮可罗宾</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -10883,7 +10883,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>山治</t>
+          <t>文斯莫克</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -11040,7 +11040,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>乔巴</t>
+          <t>托尼托尼</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -11511,7 +11511,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>善逸</t>
+          <t>我妻善逸</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12767,7 +12767,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>约尔</t>
+          <t>约尔福杰</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -12924,7 +12924,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>尤里</t>
+          <t>尤里布莱尔</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -13552,7 +13552,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>律</t>
+          <t>影山律</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -13866,7 +13866,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>松田桃太</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -14180,7 +14180,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>尼亚</t>
+          <t>江户川柯南</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -14651,7 +14651,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>温莉</t>
+          <t>温莉洛克贝尔</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -14808,7 +14808,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>罗伊</t>
+          <t>罗伊马斯坦</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -14965,7 +14965,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>格斯</t>
+          <t>近卫昴</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15436,7 +15436,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>捷度</t>
+          <t>桂雏菊</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -17748,7 +17748,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>坂本</t>
+          <t>山田太郎</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -18847,7 +18847,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>柊镜</t>
+          <t>日下部美纱绪</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -19004,7 +19004,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>柊司</t>
+          <t>樱庭光</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -22772,7 +22772,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>惠惠</t>
+          <t>泽村英梨梨</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -23400,7 +23400,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>雷姆</t>
+          <t>安娜塔西亚</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -23557,7 +23557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>拉姆</t>
+          <t>法兰黛莉卡</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -23714,7 +23714,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>桐人</t>
+          <t>优吉欧</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -24028,7 +24028,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>诗乃</t>
+          <t>桐谷直叶</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -24185,7 +24185,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>莉法</t>
+          <t>结城明日奈</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -25284,7 +25284,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>艾伦</t>
+          <t>艾伦耶格尔</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -25441,7 +25441,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>三笠</t>
+          <t>三笠阿克曼</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -26383,7 +26383,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>路飞</t>
+          <t>蒙奇路飞</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -26540,7 +26540,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>索隆</t>
+          <t>罗罗诺亚</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -26697,7 +26697,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>娜美</t>
+          <t>妮可罗宾</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -26854,7 +26854,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>山治</t>
+          <t>文斯莫克</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -27011,7 +27011,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>乔巴</t>
+          <t>托尼托尼</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -27482,7 +27482,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>善逸</t>
+          <t>我妻善逸</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -28738,7 +28738,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>约尔</t>
+          <t>约尔福杰</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -28895,7 +28895,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>尤里</t>
+          <t>尤里布莱尔</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -29523,7 +29523,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>律</t>
+          <t>影山律</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -29837,7 +29837,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>松田桃太</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -30151,7 +30151,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>尼亚</t>
+          <t>江户川柯南</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -30622,7 +30622,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>温莉</t>
+          <t>温莉洛克贝尔</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -30779,7 +30779,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>罗伊</t>
+          <t>罗伊马斯坦</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -30936,7 +30936,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>格斯</t>
+          <t>近卫昴</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -31407,7 +31407,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>捷度</t>
+          <t>桂雏菊</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -32445,7 +32445,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>坂本</t>
+          <t>山田太郎</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -32515,7 +32515,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>柊镜</t>
+          <t>日下部美纱绪</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -32525,7 +32525,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>柊司</t>
+          <t>樱庭光</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -32765,7 +32765,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>惠惠</t>
+          <t>泽村英梨梨</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -32805,7 +32805,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>雷姆</t>
+          <t>安娜塔西亚</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -32815,7 +32815,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>拉姆</t>
+          <t>法兰黛莉卡</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -32825,7 +32825,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>桐人</t>
+          <t>优吉欧</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -32845,7 +32845,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>诗乃</t>
+          <t>桐谷直叶</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -32855,7 +32855,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>莉法</t>
+          <t>结城明日奈</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -32925,7 +32925,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>艾伦</t>
+          <t>艾伦耶格尔</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -32935,7 +32935,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>三笠</t>
+          <t>三笠阿克曼</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -32995,7 +32995,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>路飞</t>
+          <t>蒙奇路飞</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -33005,7 +33005,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>索隆</t>
+          <t>罗罗诺亚</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -33015,7 +33015,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>娜美</t>
+          <t>妮可罗宾</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -33025,7 +33025,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>山治</t>
+          <t>文斯莫克</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -33035,7 +33035,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>乔巴</t>
+          <t>托尼托尼</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -33065,7 +33065,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>善逸</t>
+          <t>我妻善逸</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -33145,7 +33145,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>约尔</t>
+          <t>约尔福杰</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -33155,7 +33155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>尤里</t>
+          <t>尤里布莱尔</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -33195,7 +33195,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>律</t>
+          <t>影山律</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -33215,7 +33215,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>松田桃太</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -33235,7 +33235,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>尼亚</t>
+          <t>江户川柯南</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -33265,7 +33265,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>温莉</t>
+          <t>温莉洛克贝尔</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -33275,7 +33275,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>罗伊</t>
+          <t>罗伊马斯坦</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -33285,7 +33285,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>格斯</t>
+          <t>近卫昴</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -33315,7 +33315,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>捷度</t>
+          <t>桂雏菊</t>
         </is>
       </c>
       <c r="B96" t="n">
